--- a/tools/importer/reports/import-marketing-hub.report.xlsx
+++ b/tools/importer/reports/import-marketing-hub.report.xlsx
@@ -52,7 +52,7 @@
     <t>marketing-hub</t>
   </si>
   <si>
-    <t>2026-03-19T05:37:15.484Z</t>
+    <t>2026-03-26T08:04:43.994Z</t>
   </si>
   <si>
     <t>Banking - CommBank</t>
@@ -70,7 +70,7 @@
     <t>business</t>
   </si>
   <si>
-    <t>2026-03-19T05:37:51.122Z</t>
+    <t>2026-03-26T08:05:11.411Z</t>
   </si>
   <si>
     <t>Business Banking - CommBank</t>
@@ -88,7 +88,7 @@
     <t>digital-banking</t>
   </si>
   <si>
-    <t>2026-03-19T05:37:56.806Z</t>
+    <t>2026-03-26T08:05:18.207Z</t>
   </si>
   <si>
     <t>Digital Banking - CommBank</t>
@@ -100,13 +100,13 @@
     <t>home-buying.report.json</t>
   </si>
   <si>
-    <t>["announcement-banner","hero","promo-offer-banner","promo-offer-banner","article-cards","product-card","product-card","product-card"]</t>
+    <t>["announcement-banner","hero","anchor-tile-nav","promo-offer-banner","promo-offer-banner","article-cards","product-card","product-card","product-card"]</t>
   </si>
   <si>
     <t>home-buying</t>
   </si>
   <si>
-    <t>2026-03-19T05:37:22.017Z</t>
+    <t>2026-03-26T23:32:07.291Z</t>
   </si>
   <si>
     <t>Home loans, interest rates, calculators &amp; offers | CommBank</t>
@@ -124,7 +124,7 @@
     <t>index</t>
   </si>
   <si>
-    <t>2026-03-19T06:54:46.152Z</t>
+    <t>2026-03-26T23:32:42.893Z</t>
   </si>
   <si>
     <t>CommBank - bank accounts, credit cards, home loans and insurance</t>
@@ -139,7 +139,7 @@
     <t>institutional</t>
   </si>
   <si>
-    <t>2026-03-19T05:38:03.654Z</t>
+    <t>2026-03-26T08:05:24.996Z</t>
   </si>
   <si>
     <t>Institutional - CommBank</t>
@@ -157,7 +157,7 @@
     <t>insurance</t>
   </si>
   <si>
-    <t>2026-03-19T05:37:26.572Z</t>
+    <t>2026-03-26T08:04:57.830Z</t>
   </si>
   <si>
     <t>Insurance - CommBank</t>
@@ -175,7 +175,7 @@
     <t>investing-and-super</t>
   </si>
   <si>
-    <t>2026-03-19T05:37:45.043Z</t>
+    <t>2026-03-26T08:05:05.549Z</t>
   </si>
   <si>
     <t>Investing &amp; Super - CommBank</t>
